--- a/docs/javni-sajt/SLIKE_ZA_PRONALAZENJE.xlsx
+++ b/docs/javni-sajt/SLIKE_ZA_PRONALAZENJE.xlsx
@@ -73,7 +73,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -90,6 +90,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -455,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -494,195 +495,221 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>To su baze sa sistemskih strana Line 30 (17 × 1 L) i Line 35 (17 × 1 L + 32 × 0,5 L). Nisu posebni proizvodi bez slike: baze se kupcu prikazuju na sistemskoj strani, a nedostaje jedna fotografija generičke limenke po pakovanju. Isti nalaz je već evidentiran kao 3 slota ambalaže (OLD-043…045). Zato su u glavnom spisku 3 reda (plus 4 za Line 45), a ne 66 zadataka. Nisu ponovljeni nalazi među 189 — preklapanje je 0.</t>
+          <t>To su baze sa sistemskih strana Line 30 (17 × 1 L) i Line 35 (17 × 1 L + 32 × 0,5 L). Nisu posebni proizvodi bez slike: baze se kupcu prikazuju na sistemskoj strani, a nedostaje jedna fotografija generičke limenke po pakovanju. Isti nalaz je već evidentiran kao 3 slota ambalaže (OLD-043…045): 66 varijanti = 3 potrebne fotografije (Line 30 1 L: 17, Line 35 1 L: 17, Line 35 0,5 L: 32). Sa Line 45 (68 baza, prikazuje se primer limenke) ukupno 134 baze = 7 fotografija. Mapiranje svake varijante je na listu „baslac ambalaža po zapremini”. Nisu ponovljeni nalazi među 189 — preklapanje je 0.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr"/>
-      <c r="B5" s="2" t="n"/>
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>FO-314</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Prebačeno u „čeka potvrdu identiteta”: etiketa ne nosi šifru ni nijansu, Brand Kit isti fajl nosi i kao FO-313 (zvanični FO-313 je Cherry Dark), a poklopac je crven, bliži FO-312/313 nego pink nijansama 308–310.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Stanje</t>
+          <t>Cosmos Brand Kit — pravo</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Broj</t>
+          <t>ISPRAVKA: ranije označeno kao potvrđeno. Brand Kit je zvaničan izvor (742 objavljene slike), ali pisana dozvola za web upotrebu nije dokumentovana — vidi nacrt zahteva Cosmos Lac-u.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>135</v>
+          <t>Pregled sa slikama</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/PREGLED_SPORNIH_SLIKA.html (i .jpg): 8 Cosmos sa zajedničkom slikom, 7 SATA sa slikom srodnog artikla, FO-314; neslaganje 175/185 ml za Chrome 450 / Gold 451 je istaknuto — katalog NIJE menjan.</t>
+        </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="A8" s="1" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>nije pronađeno — placeholder prihvaćen</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>12</v>
+          <t>Stanje</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Broj</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>nije pronađeno — potrebna Vaša fotografija</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>čeka potvrdu identiteta</t>
+          <t>nije pronađeno — placeholder prihvaćen</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>pronađeno — spremno za uvoz (pravo: Brand Kit)</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr"/>
-      <c r="B14" s="2" t="n"/>
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>Po brendu</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Stanja</t>
-        </is>
+          <t>čeka potvrdu identiteta</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>R-M</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija: 15; čeka potvrdu identiteta: 1; pronađeno — čeka pravo: 1</t>
-        </is>
-      </c>
+      <c r="A16" s="1" t="inlineStr"/>
+      <c r="B16" s="2" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>baslac</t>
+          <t>Po brendu</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>čeka potvrdu identiteta: 1; nije pronađeno — potrebna Vaša fotografija: 3</t>
+          <t>Stanja</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>Norbin</t>
+          <t>R-M</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija: 4</t>
+          <t>nije pronađeno — potrebna Vaša fotografija: 15; čeka potvrdu identiteta: 1; pronađeno — čeka pravo: 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>Cosmos Lac</t>
+          <t>baslac</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici: 8; pronađeno — čeka pravo: 1; pronađeno — spremno za uvoz (pravo: Brand Kit): 2</t>
+          <t>čeka potvrdu identiteta: 1; nije pronađeno — potrebna Vaša fotografija: 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>Norbin</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo: 133; nije pronađeno — placeholder prihvaćen: 12; pronađeno — čeka pravo i potvrdu varijante: 7; nije pronađeno — potrebna Vaša fotografija: 1</t>
+          <t>nije pronađeno — potrebna Vaša fotografija: 4</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr"/>
-      <c r="B21" s="2" t="n"/>
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>Cosmos Lac</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici: 8; pronađeno — čeka pravo: 2; čeka potvrdu identiteta: 1</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
+          <t>SATA</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>pronađeno — čeka pravo: 133; nije pronađeno — placeholder prihvaćen: 12; pronađeno — čeka pravo i potvrdu varijante: 7; nije pronađeno — potrebna Vaša fotografija: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr"/>
+      <c r="B23" s="2" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
           <t>Gde su fajlovi</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/&lt;brend&gt;/ — van git-a, nije objavljeno. SATA _manifest.json ima URL, SHA-256 i stranicu artikla za svaki fajl.</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>Pravila</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Podudaranje „Potvrđeno” samo kad slika nosi tačnu šifru/naziv ili je sopstvena glavna slika artikla na stranici proizvođača. Zajednička slika porodice je označena posebno. Šifre se ne izmišljaju.</t>
         </is>
@@ -2564,7 +2591,7 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -2585,7 +2612,7 @@
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
@@ -2610,7 +2637,7 @@
       </c>
       <c r="S27" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2682,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -2676,7 +2703,7 @@
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
@@ -2701,7 +2728,7 @@
       </c>
       <c r="S28" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2773,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -2767,7 +2794,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
@@ -2792,7 +2819,7 @@
       </c>
       <c r="S29" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2864,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -2858,7 +2885,7 @@
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -2883,7 +2910,7 @@
       </c>
       <c r="S30" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3041,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Potvrđeno — zvanična slika sa stranice FO-314 na cosmoslac.com i iz Brand Kit-a (FLAME ORANGE 400 ml); napomena: Brand Kit isti fajl nosi i pod nazivom FO-313</t>
+          <t>ČEKA POTVRDU — etiketa ne prikazuje šifru ni nijansu; stranica FO-314 na cosmoslac.com koristi ovaj fajl, ali Brand Kit isti fajl nosi i kao „fo-313-Piglet-Pink-Dark” (zvanični FO-313 je Cherry Dark, drugi fajl); poklopac je crven, bliži FO-312/313 nego „pink” nijansama 308–310 — podudaranje nije dokazano</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike)</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3040,7 +3067,7 @@
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Potvrda prava: pisana dozvola Cosmos Lac ili dopuna Brand Kit-a</t>
+          <t>Potvrda Cosmos Lac-a: koja je slika FO-314 Piglet Pink Dark</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
@@ -3065,7 +3092,7 @@
       </c>
       <c r="S32" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — spremno za uvoz (pravo: Brand Kit)</t>
+          <t>čeka potvrdu identiteta</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3137,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -3131,7 +3158,7 @@
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
@@ -3156,7 +3183,7 @@
       </c>
       <c r="S33" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3228,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -3222,7 +3249,7 @@
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
@@ -3247,7 +3274,7 @@
       </c>
       <c r="S34" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -3292,7 +3319,7 @@
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -3313,7 +3340,7 @@
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
@@ -3338,7 +3365,7 @@
       </c>
       <c r="S35" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3410,7 @@
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike) — za ovu sliku potvrdite i nijansu/pakovanje</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a — za ovu sliku potvrdite i nijansu/pakovanje</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -3404,7 +3431,7 @@
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu)</t>
+          <t>Odluka: prihvatate li zajedničku sliku porodice (ne prikazuje varijantu) + potvrda prava Brand Kit-a</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
@@ -3429,7 +3456,7 @@
       </c>
       <c r="S36" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
         </is>
       </c>
     </row>
@@ -3470,7 +3497,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>DA — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene Cosmos slike)</t>
+          <t>NIJE DOKUMENTOVANO — zvanični Cosmos Brand Kit (isti izvor kao 742 objavljene slike), ali pisana dozvola za web upotrebu ne postoji u dokumentaciji, a izvorni ZIP-ovi više nisu u Downloads; potrebna potvrda Cosmos Lac-a</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -3491,7 +3518,7 @@
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Potvrda prava: pisana dozvola Cosmos Lac ili dopuna Brand Kit-a</t>
+          <t>Potvrda prava Brand Kit-a (Cosmos Lac)</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
@@ -3516,7 +3543,7 @@
       </c>
       <c r="S37" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — spremno za uvoz (pravo: Brand Kit)</t>
+          <t>pronađeno — čeka pravo</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6733,7 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-shaker-ring-rps-the-original__117051.webp</t>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-shaker-ring-rps-the-original__glavni-117051__slika-srodnog-173435.webp</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
@@ -6736,7 +6763,7 @@
       </c>
       <c r="R72" s="5" t="inlineStr">
         <is>
-          <t>sata__sata-shaker-ring-rps-the-original__117051.webp</t>
+          <t>sata__sata-shaker-ring-rps-the-original__glavni-117051__slika-srodnog-173435.webp</t>
         </is>
       </c>
       <c r="S72" s="5" t="inlineStr">
@@ -8016,7 +8043,7 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-material-hose__49155.webp</t>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-material-hose__glavni-49155__slika-srodnog-49999.webp</t>
         </is>
       </c>
       <c r="M86" s="2" t="inlineStr">
@@ -8046,7 +8073,7 @@
       </c>
       <c r="R86" s="5" t="inlineStr">
         <is>
-          <t>sata__sata-material-hose__49155.webp</t>
+          <t>sata__sata-material-hose__glavni-49155__slika-srodnog-49999.webp</t>
         </is>
       </c>
       <c r="S86" s="5" t="inlineStr">
@@ -8111,7 +8138,7 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-air-hose__4754.webp</t>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-air-hose__glavni-4754__slika-srodnog-9902.webp</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
@@ -8141,7 +8168,7 @@
       </c>
       <c r="R87" s="5" t="inlineStr">
         <is>
-          <t>sata__sata-air-hose__4754.webp</t>
+          <t>sata__sata-air-hose__glavni-4754__slika-srodnog-9902.webp</t>
         </is>
       </c>
       <c r="S87" s="5" t="inlineStr">
@@ -9821,7 +9848,7 @@
       </c>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-lackierpistolenkoffer__1172.webp</t>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-lackierpistolenkoffer__glavni-1172__slika-srodnog-153288.webp</t>
         </is>
       </c>
       <c r="M105" s="2" t="inlineStr">
@@ -9851,7 +9878,7 @@
       </c>
       <c r="R105" s="5" t="inlineStr">
         <is>
-          <t>sata__sata-lackierpistolenkoffer__1172.webp</t>
+          <t>sata__sata-lackierpistolenkoffer__glavni-1172__slika-srodnog-153288.webp</t>
         </is>
       </c>
       <c r="S105" s="5" t="inlineStr">
@@ -10676,7 +10703,7 @@
       </c>
       <c r="L114" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-luftmikrometer__9860.webp</t>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-luftmikrometer__glavni-9860__slika-srodnog-27771.webp</t>
         </is>
       </c>
       <c r="M114" s="2" t="inlineStr">
@@ -10706,7 +10733,7 @@
       </c>
       <c r="R114" s="5" t="inlineStr">
         <is>
-          <t>sata__sata-luftmikrometer__9860.webp</t>
+          <t>sata__sata-luftmikrometer__glavni-9860__slika-srodnog-27771.webp</t>
         </is>
       </c>
       <c r="S114" s="5" t="inlineStr">
@@ -10771,7 +10798,7 @@
       </c>
       <c r="L115" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-mini-set-2__21733.webp</t>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-mini-set-2__glavni-21733__slika-srodnog-56408.webp</t>
         </is>
       </c>
       <c r="M115" s="2" t="inlineStr">
@@ -10801,7 +10828,7 @@
       </c>
       <c r="R115" s="5" t="inlineStr">
         <is>
-          <t>sata__sata-mini-set-2__21733.webp</t>
+          <t>sata__sata-mini-set-2__glavni-21733__slika-srodnog-56408.webp</t>
         </is>
       </c>
       <c r="S115" s="5" t="inlineStr">
@@ -13806,7 +13833,7 @@
       </c>
       <c r="L148" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-vario-top-spray__56010.webp</t>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/sata/sata__sata-vario-top-spray__glavni-56010__slika-srodnog-61507.webp</t>
         </is>
       </c>
       <c r="M148" s="2" t="inlineStr">
@@ -13836,7 +13863,7 @@
       </c>
       <c r="R148" s="5" t="inlineStr">
         <is>
-          <t>sata__sata-vario-top-spray__56010.webp</t>
+          <t>sata__sata-vario-top-spray__glavni-56010__slika-srodnog-61507.webp</t>
         </is>
       </c>
       <c r="S148" s="5" t="inlineStr">
@@ -19694,447 +19721,6031 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:H148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="60" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="36" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Slotovi: BROJ VARIJANTI ≠ BROJ POTREBNIH FOTOGRAFIJA. Svaka fotografija je jedna generička limenka sistema u datoj zapremini; baze se razlikuju šifrom i nijansom, ne limenkom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Slot fotografije</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Sistem</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Pakovanje</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
-        <is>
-          <t>Baza (varijanti)</t>
-        </is>
-      </c>
-      <c r="E1" s="3" t="inlineStr">
-        <is>
-          <t>Šta nedostaje</t>
-        </is>
-      </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>Varijanti (baza) u slotu</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Od toga u spisku od 66 (bez ikakve slike)</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>Potrebnih različitih fotografija</t>
+        </is>
+      </c>
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>Postojeći materijal</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
-        <is>
-          <t>1. Pronađeno</t>
-        </is>
-      </c>
-      <c r="H1" s="3" t="inlineStr">
-        <is>
-          <t>2. Podudaranje</t>
-        </is>
-      </c>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>3. Pravo</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="H3" s="3" t="inlineStr">
         <is>
           <t>Potrebno od Vas</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Na Surventis portalu postoji sopstveni 1 L packshot SAMO za bazu 30-S110 (asset 12114) — pokriva tu jednu varijantu, ne slot</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>Jedna fotografija prazne/generičke limenke Line 30 1 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Generička limenka ove zapremine ne postoji na portalu</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Jedna fotografija prazne/generičke limenke Line 35 1 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Generička limenka ove zapremine ne postoji na portalu</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Jedna fotografija prazne/generičke limenke Line 35 0,5 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>F-45-5L</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5 L</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Prikazuje se primer limenke 45-W (druga zapremina); tačna zapremina nedostaje</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Jedna fotografija prazne/generičke limenke Line 45 5 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Generička „45-W” limenka koju je vlasnik dostavio (prikazuje se kao primer)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Jedna fotografija prazne/generičke limenke Line 45 1 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Prikazuje se primer limenke 45-W (druga zapremina); tačna zapremina nedostaje</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>Jedna fotografija prazne/generičke limenke Line 45 0,5 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Prikazuje se primer limenke 45-W (druga zapremina); tačna zapremina nedostaje</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>Jedna fotografija prazne/generičke limenke Line 45 0,1 L</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>UKUPNO</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr"/>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="n">
+        <v>134</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Mapiranje varijanti na slotove (sve baze sistemskih strana; kolona „u spisku 66” označava redove iz spiska druge sesije)</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
+      <c r="E13" s="2" t="n"/>
+      <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Sistem</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>Pakovanje</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>Slot fotografije</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>Šifra baze</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="inlineStr">
+        <is>
+          <t>Naziv</t>
+        </is>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>Link (varijanta)</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Zapis bez ikakve slike</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>U spisku 66</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>Line 30</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>1 L</t>
         </is>
       </c>
-      <c r="D2" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>Fotografija PRAZNE/generičke limenke Line 30 1 L — ne fotografija pojedinačne baze (baze se razlikuju šifrom i nijansom, ne limenkom)</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Ima: 30-S110 (1 L) — sopstveni packshot te baze na Surventis portalu (asset 12114); generička 1 L limenka sistema ne postoji</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Jedna Vaša fotografija limenke Line 30 1 L pokriva svih 17 baza</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija (1 snimak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>30-S110</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S110 Yellow Green</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S110</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>30-S120</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S120 Yellow bright</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S120</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>30-S150</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S150 Orange light</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S150</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30-S160</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S160 Yellow dark</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S160</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>30-S220</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S220 Orange</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S220</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>30-S230</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S230 Red light</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S230</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>30-S310</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S310 Red Brown</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S310</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>30-S320</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S320 Red bright</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S320</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>30-S330</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S330 Red Purple</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S330</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>30-S411</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S411 Purple</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S411</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>30-S420</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S420 Red</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S420</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>30-S511</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S511 Blue Red</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S511</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>30-S520</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S520 Blue Green</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S520</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>30-S530</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S530 Blue</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S530</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>30-S610</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S610 Green Blue</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S610</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>30-S621</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S621 Green Yellow</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S621</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Line 30</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>F-30-1L</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>30-S910</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 30-S910 Black</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-30?varijanta=30-S910</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>Line 35</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>1 L</t>
         </is>
       </c>
-      <c r="D3" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>Fotografija PRAZNE/generičke limenke Line 35 1 L — ne fotografija pojedinačne baze (baze se razlikuju šifrom i nijansom, ne limenkom)</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Portal nema generičku 1 L limenku</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Jedna Vaša fotografija limenke Line 35 1 L pokriva svih 17 baza</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija (1 snimak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>35-M1021</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1021 White blue flip</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1021</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>Line 35</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>35-M1110</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1110 Yellow Gold</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1110</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>0,5 L</t>
         </is>
       </c>
-      <c r="D4" s="2" t="n">
-        <v>32</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Fotografija PRAZNE/generičke limenke Line 35 0,5 L — ne fotografija pojedinačne baze (baze se razlikuju šifrom i nijansom, ne limenkom)</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Portal nema generičku 0,5 L limenku</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Jedna Vaša fotografija limenke Line 35 0,5 L pokriva svih 32 baza</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija (1 snimak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>35-M1120</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1120 Yellow Ochre</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1120</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>35-M1130</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1130 Yellow Green</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1130</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>35-M1140</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1140 Yellow Light</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1140</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>35-M1150</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1150 Yellow</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1150</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>35-M1160</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1160 Orange</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1160</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>35-M1170</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1170 Yellow shine</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1170</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>35-M1220</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1220 Orange light</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1220</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>35-M1230</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1230 Orange Transparent</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1230</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>35-M1310</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1310 Red transparent</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1310</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>35-M1320</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1320 Red</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1320</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>35-M1330</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1330 Red Orange</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1330</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>35-M1340</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1340 Red bright</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1340</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>35-M1350</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1350 Red dark</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1350</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>35-M1360</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1360 Red light</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1360</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>35-M1370</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1370 Red Blue</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1370</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>35-M1390</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1390 Pure Red</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1390</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>35-M1411</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1411 Bluish violett</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1411</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>35-M1420</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1420 Purple Red</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1420</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>35-M1430</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1430 Red Purple</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1430</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>35-M1511</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1511 Blue</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1511</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>35-M1516</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1516 Blue light</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1516</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>35-M1521</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1521 Blue Green</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1521</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>35-M1530</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1530 Blue transparent</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1530</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>35-M1610</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1610 Green Blue</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1610</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>35-M1920</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1920 Black Blue</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1920</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>35-M1990</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M1990 Black Graphite</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M1990</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>35-M211</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M211 Silver Alu fine extra</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M211</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>35-M215</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M215 Silver Crystal fine</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M215</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>35-M216</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M216 Silver Alu coarse</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M216</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>35-M217</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M217 Silver Crystal coarse</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M217</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>35-M218</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M218 Silver Dollar fine</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M218</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>35-M300</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M300 Fine Pearl White</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M300</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>35-M302</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M302 Pearl White coarse</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M302</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>35-M311</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M311 Pearl Yellow</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M311</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>35-M312</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M312 Pearl Green Red</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M312</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>35-M313</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M313 Pearl Gold</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M313</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>35-M331</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M331 Red Xirallic</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M331</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>35-M332</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M332 Pearl Red</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M332</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>35-M341</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M341 Pearl Purple</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M341</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>35-M343</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M343 Pearl Red Brown</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M343</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>35-M352</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M352 Pearl Blue Fine</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M352</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>35-M353</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M353 Pearl Green Blue</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M353</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>35-M381</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M381 Pearl Copper</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M381</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>35-M382</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M382 Pearl Red fine</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M382</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>35-M391</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M391 Pearl Silver Xirallic</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M391</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>F-35-1L</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>35-M590</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M590 Pure Black</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M590</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Line 35</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>F-35-05L</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>35-M599</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 35-M599 Chrome</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-35?varijanta=35-M599</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>da</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>DA</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>5 L</t>
         </is>
       </c>
-      <c r="D5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>Fotografija PRAZNE/generičke limenke Line 45 5 L — ne fotografija pojedinačne baze (baze se razlikuju šifrom i nijansom, ne limenkom)</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Portal nema generičku 5 L limenku</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Jedna Vaša fotografija limenke Line 45 5 L pokriva svih 2 baza</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija (1 snimak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>F-45-5L</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>45-W00</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W00 Converter Water</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W00</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>1 L</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Fotografija PRAZNE/generičke limenke Line 45 1 L — ne fotografija pojedinačne baze (baze se razlikuju šifrom i nijansom, ne limenkom)</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Primer limenke linije 1 L (prikazuje se uz napomenu)</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Jedna Vaša fotografija limenke Line 45 1 L pokriva svih 7 baza</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija (1 snimak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>45-W05</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W05 Effect Additive</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W05</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>45-W1010</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1010 Basecoat AU White</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1010</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>45-W1011</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1011 Basecoat AU White Frost</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1011</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>0,5 L</t>
         </is>
       </c>
-      <c r="D7" s="2" t="n">
-        <v>49</v>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>Fotografija PRAZNE/generičke limenke Line 45 0,5 L — ne fotografija pojedinačne baze (baze se razlikuju šifrom i nijansom, ne limenkom)</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Portal nema generičku 0,5 L limenku</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Jedna Vaša fotografija limenke Line 45 0,5 L pokriva svih 49 baza</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija (1 snimak)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>45-W1012</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1012 Basecoat</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1012</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>Line 45</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>45-W1019</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1019 Basecoat AU White Light</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1019</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>45-W1020</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1020 Basecoat AU White blue flip</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1020</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>45-W1110</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1110 Basecoat AU Yellow Gold</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1110</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>45-W1120</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1120 Basecoat Yellow Ocre</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1120</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>45-W1130</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1130 Basecoat AU Yellow Green</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1130</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>45-W1140</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1140 Basecoat AU Yellow light</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1140</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>45-W1147</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1147 Basecoat Yellow Lime</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1147</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>45-W1150</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1150 Basecoat AU Yellow</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1150</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>45-W1160</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1160 Basecoat AU Orange</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1160</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>45-W1220</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1220 Basecoat AU Orange light</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1220</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>45-W1310</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1310 Basecoat AU Red transparent</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1310</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>45-W1320</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1320 Basecoat Red</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1320</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>45-W1340</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1340 Basecoat AU Red bright</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1340</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>45-W1350</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1350 Basecoat AU Red dark</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1350</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>45-W1360</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1360 Basecoat AU Red light</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1360</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>45-W1371</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1371 Basecoat Red Blue</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1371</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>0,1 L</t>
         </is>
       </c>
-      <c r="D8" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>Fotografija PRAZNE/generičke limenke Line 45 0,1 L — ne fotografija pojedinačne baze (baze se razlikuju šifrom i nijansom, ne limenkom)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Portal nema generičku 0,1 L limenku</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Ne</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Jedna Vaša fotografija limenke Line 45 0,1 L pokriva svih 12 baza</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija (1 snimak)</t>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>45-W1390</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1390 Basecoat Red Shining</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1390</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>45-W1411</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1411 Basecoat AU Bluish violett</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1411</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>45-W1420</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1420 Basecoat AU Purple Red</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1420</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>45-W1430</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1430 Basecoat Red Purple</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1430</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>45-W1510</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1510 Basecoat Blue Light</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1510</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>45-W1520</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1520 Basecoat AU Blue Green</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1520</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>45-W1530</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1530 Basecoat AU Blue transparent</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1530</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>45-W1610</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1610 Basecoat Green Blue</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1610</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>45-W1621</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1621 Basecoat AU Green Yellow</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1621</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>45-W1910</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1910 Basecoat Black Yellow</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1910</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>45-W1920</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1920 Basecoat AU Black</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1920</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>45-W1921</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1921 Basecoat AU Black Light</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1921</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>45-W1930</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1930 Basecoat Black Blue</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1930</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>45-W1990</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W1990 Basecoat Black Graphite</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W1990</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>45-W210</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W210 Basecoat AU Silver Alu Perfect</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W210</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>45-W211</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W211 Basecoat AU Silver Alu fine extra</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W211</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>45-W212</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W212 Basecoat AU Silver Alu fine</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W212</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>45-W213</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W213 Basecoat AU Silver Alu</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W213</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H119" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
+        <is>
+          <t>45-W214</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W214 Basecoat Silver dollar bright</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W214</t>
+        </is>
+      </c>
+      <c r="G120" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H120" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
+        <is>
+          <t>45-W220</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W220 Basecoat Silver Crystal fine</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W220</t>
+        </is>
+      </c>
+      <c r="G121" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H121" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
+        <is>
+          <t>45-W221</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W221 Basecoat Silver Crystal coarse</t>
+        </is>
+      </c>
+      <c r="F122" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W221</t>
+        </is>
+      </c>
+      <c r="G122" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>45-W301</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W301 Basecoat AU Pearl White</t>
+        </is>
+      </c>
+      <c r="F123" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W301</t>
+        </is>
+      </c>
+      <c r="G123" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
+        <is>
+          <t>45-W302</t>
+        </is>
+      </c>
+      <c r="E124" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W302 Basecoat AU Pearl White coarse</t>
+        </is>
+      </c>
+      <c r="F124" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W302</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
+        <is>
+          <t>45-W311</t>
+        </is>
+      </c>
+      <c r="E125" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W311 Basecoat AU Pearl Yellow</t>
+        </is>
+      </c>
+      <c r="F125" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W311</t>
+        </is>
+      </c>
+      <c r="G125" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H125" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>45-W331</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W331 Basecoat Pearl Red Xirallic</t>
+        </is>
+      </c>
+      <c r="F126" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W331</t>
+        </is>
+      </c>
+      <c r="G126" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H126" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
+        <is>
+          <t>45-W343</t>
+        </is>
+      </c>
+      <c r="E127" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W343 Basecoat AU Pearl Red Brown</t>
+        </is>
+      </c>
+      <c r="F127" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W343</t>
+        </is>
+      </c>
+      <c r="G127" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H127" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
+        <is>
+          <t>45-W351</t>
+        </is>
+      </c>
+      <c r="E128" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W351 Basecoat Pearl Blue</t>
+        </is>
+      </c>
+      <c r="F128" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W351</t>
+        </is>
+      </c>
+      <c r="G128" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H128" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
+        <is>
+          <t>45-W352</t>
+        </is>
+      </c>
+      <c r="E129" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W352 Basecoat AU Pearl Blue fine</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W352</t>
+        </is>
+      </c>
+      <c r="G129" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H129" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
+        <is>
+          <t>45-W382</t>
+        </is>
+      </c>
+      <c r="E130" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W382 Basecoat AU Pearl Red fine</t>
+        </is>
+      </c>
+      <c r="F130" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W382</t>
+        </is>
+      </c>
+      <c r="G130" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H130" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
+        <is>
+          <t>45-W391</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W391 Basecoat Pearl Silver Xirallic</t>
+        </is>
+      </c>
+      <c r="F131" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W391</t>
+        </is>
+      </c>
+      <c r="G131" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H131" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>45-W400</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W400 Basecoat AU Pearl Fine White</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W400</t>
+        </is>
+      </c>
+      <c r="G132" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H132" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
+        <is>
+          <t>45-W435</t>
+        </is>
+      </c>
+      <c r="E133" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W435 Basecoat AU Pearl Red Shine</t>
+        </is>
+      </c>
+      <c r="F133" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W435</t>
+        </is>
+      </c>
+      <c r="G133" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H133" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
+        <is>
+          <t>45-W446</t>
+        </is>
+      </c>
+      <c r="E134" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W446 Basecoat AU Pearl Purple</t>
+        </is>
+      </c>
+      <c r="F134" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W446</t>
+        </is>
+      </c>
+      <c r="G134" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H134" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
+        <is>
+          <t>45-W485</t>
+        </is>
+      </c>
+      <c r="E135" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W485 Basecoat AU Pearl Copper</t>
+        </is>
+      </c>
+      <c r="F135" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W485</t>
+        </is>
+      </c>
+      <c r="G135" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H135" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>0,5 L</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>F-45-05L</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
+        <is>
+          <t>45-W490</t>
+        </is>
+      </c>
+      <c r="E136" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W490 Basecoat AU Pearl Gold</t>
+        </is>
+      </c>
+      <c r="F136" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W490</t>
+        </is>
+      </c>
+      <c r="G136" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H136" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>1 L</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>F-45-1L</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
+        <is>
+          <t>45-W590</t>
+        </is>
+      </c>
+      <c r="E137" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W590 Basecoat</t>
+        </is>
+      </c>
+      <c r="F137" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W590</t>
+        </is>
+      </c>
+      <c r="G137" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H137" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>45-W599</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 45-W599 Basecoat AU Chrome</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=45-W599</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>49-W408</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W408 Basecoat Transparent Sparkle</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W408</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>49-W410</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W410 Basecoat AU Pearl Gold</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W410</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
+        <is>
+          <t>49-W420</t>
+        </is>
+      </c>
+      <c r="E141" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W420 Basecoat AU Pearl Bronze</t>
+        </is>
+      </c>
+      <c r="F141" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W420</t>
+        </is>
+      </c>
+      <c r="G141" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H141" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
+        <is>
+          <t>49-W425</t>
+        </is>
+      </c>
+      <c r="E142" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W425 Basecoat AU Pearl Mandarin</t>
+        </is>
+      </c>
+      <c r="F142" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W425</t>
+        </is>
+      </c>
+      <c r="G142" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H142" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
+        <is>
+          <t>49-W436</t>
+        </is>
+      </c>
+      <c r="E143" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W436 Basecoat AU Pearl Green Red</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W436</t>
+        </is>
+      </c>
+      <c r="G143" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H143" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>49-W441</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W441 Basecoat AU Pearl Violet White</t>
+        </is>
+      </c>
+      <c r="F144" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W441</t>
+        </is>
+      </c>
+      <c r="G144" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H144" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
+        <is>
+          <t>49-W443</t>
+        </is>
+      </c>
+      <c r="E145" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W443 Basecoat AU Pearl Violet</t>
+        </is>
+      </c>
+      <c r="F145" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W443</t>
+        </is>
+      </c>
+      <c r="G145" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H145" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
+        <is>
+          <t>49-W448</t>
+        </is>
+      </c>
+      <c r="E146" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W448 Basecoat AU Pearl Purple Red</t>
+        </is>
+      </c>
+      <c r="F146" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W448</t>
+        </is>
+      </c>
+      <c r="G146" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H146" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>49-W469</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W469 Basecoat AU Pearl Green Blue</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W469</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>Line 45</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>0,1 L</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>F-45-01L</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>49-W488</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Baslac 49-W488 Basecoat AU Pearl Copper Coarse</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>https://carsystemirm.com/proizvodi/grupa/baslac-line-45?varijanta=49-W488</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr">
+        <is>
+          <t>ne (prikazuje se primer limenke linije 45-W)</t>
+        </is>
+      </c>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>ne</t>
         </is>
       </c>
     </row>

--- a/docs/javni-sajt/SLIKE_ZA_PRONALAZENJE.xlsx
+++ b/docs/javni-sajt/SLIKE_ZA_PRONALAZENJE.xlsx
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B25"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -526,190 +526,236 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Pregled sa slikama</t>
+          <t>Ponuda i magacin</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/PREGLED_SPORNIH_SLIKA.html (i .jpg): 8 Cosmos sa zajedničkom slikom, 7 SATA sa slikom srodnog artikla, FO-314; neslaganje 175/185 ml za Chrome 450 / Gold 451 je istaknuto — katalog NIJE menjan.</t>
+          <t>Za 25 proizvoda bez pronađene slike ponuda nije potvrđena; odsustvo iz pregledanog šifarnika NE znači uklanjanje sa sajta. Trenutno stanje magacina je nepoznato dok ga vlasnik ne proveri (spisak: MAGACIN_PROVERA.xlsx, privatno).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr"/>
-      <c r="B8" s="2" t="n"/>
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Sistemi bez šifre</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>AGILIS X-TREME i ONYX HD TROPICAL: nema zahteva za fotografiju jedne ambalaže — traži se odluka o prikazu sistema.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Stanje</t>
+          <t>SATA — slike srodnih artikala</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Broj</t>
+          <t>7 slika su samo kandidati: ne uvoze se dok se ne potvrdi šta tačno prikazuju (i dok nema prava).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>136</v>
+          <t>Pregled sa slikama</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/PREGLED_SPORNIH_SLIKA.html (i .jpg): 8 Cosmos sa zajedničkom slikom, 7 SATA sa slikom srodnog artikla, FO-314; neslaganje 175/185 ml za Chrome 450 / Gold 451 je istaknuto — katalog NIJE menjan.</t>
+        </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>23</v>
-      </c>
+      <c r="A11" s="1" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>nije pronađeno — placeholder prihvaćen</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>12</v>
+          <t>Stanje</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Broj</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
+          <t>pronađeno — čeka pravo</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>8</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>čeka potvrdu identiteta</t>
+          <t>nije pronađeno — placeholder prihvaćen</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr"/>
-      <c r="B16" s="2" t="n"/>
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>Po brendu</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>Stanja</t>
-        </is>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>R-M</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija: 15; čeka potvrdu identiteta: 1; pronađeno — čeka pravo: 1</t>
-        </is>
+          <t>čeka potvrdu identiteta</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>baslac</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>čeka potvrdu identiteta: 1; nije pronađeno — potrebna Vaša fotografija: 3</t>
-        </is>
+          <t>nije pronađeno — čeka odluku o prikazu sistema</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>Norbin</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>nije pronađeno — potrebna Vaša fotografija: 4</t>
-        </is>
-      </c>
+      <c r="A20" s="1" t="inlineStr"/>
+      <c r="B20" s="2" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>Cosmos Lac</t>
+          <t>Po brendu</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici: 8; pronađeno — čeka pravo: 2; čeka potvrdu identiteta: 1</t>
+          <t>Stanja</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>SATA</t>
+          <t>R-M</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo: 133; nije pronađeno — placeholder prihvaćen: 12; pronađeno — čeka pravo i potvrdu varijante: 7; nije pronađeno — potrebna Vaša fotografija: 1</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi): 13; nije pronađeno — čeka odluku o prikazu sistema: 2; čeka potvrdu identiteta: 1; pronađeno — čeka pravo: 1</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr"/>
-      <c r="B23" s="2" t="n"/>
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>baslac</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>čeka potvrdu identiteta: 1; nije pronađeno — potrebna Vaša fotografija (ako je u ponudi): 3</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Gde su fajlovi</t>
+          <t>Norbin</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/&lt;brend&gt;/ — van git-a, nije objavljeno. SATA _manifest.json ima URL, SHA-256 i stranicu artikla za svaki fajl.</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi): 4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
+          <t>Cosmos Lac</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>pronađeno — čeka pravo i Vašu odluku o zajedničkoj slici: 8; pronađeno — čeka pravo: 2; čeka potvrdu identiteta: 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>SATA</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>pronađeno — čeka pravo: 133; nije pronađeno — placeholder prihvaćen: 12; kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo: 7; nije pronađeno — potrebna Vaša fotografija (ako je u ponudi): 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr"/>
+      <c r="B27" s="2" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Gde su fajlovi</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>~/Carsystem/radno/slike-za-pronalazenje/preuzeto/&lt;brend&gt;/ — van git-a, nije objavljeno. SATA _manifest.json ima URL, SHA-256 i stranicu artikla za svaki fajl.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
           <t>Pravila</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>Podudaranje „Potvrđeno” samo kad slika nosi tačnu šifru/naziv ili je sopstvena glavna slika artikla na stranici proizvođača. Zajednička slika porodice je označena posebno. Šifre se ne izmišljaju.</t>
         </is>
@@ -893,7 +939,7 @@
       <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
@@ -910,7 +956,7 @@
       <c r="R2" s="5" t="inlineStr"/>
       <c r="S2" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -956,7 +1002,7 @@
       <c r="M3" s="2" t="inlineStr"/>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Odluka o prikazu SISTEMA AGILIS X-TREME (nema jednu ambalažu): npr. bez fotografije, zvanična slika sistema/kolekcije ili konkretna komponenta — NE fotografisati jednu limenku</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
@@ -973,7 +1019,7 @@
       <c r="R3" s="5" t="inlineStr"/>
       <c r="S3" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — čeka odluku o prikazu sistema</t>
         </is>
       </c>
     </row>
@@ -1090,7 +1136,7 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
@@ -1107,7 +1153,7 @@
       <c r="R5" s="5" t="inlineStr"/>
       <c r="S5" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1203,7 @@
       <c r="M6" s="2" t="inlineStr"/>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1174,7 +1220,7 @@
       <c r="R6" s="5" t="inlineStr"/>
       <c r="S6" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1361,7 @@
       <c r="M8" s="2" t="inlineStr"/>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1332,7 +1378,7 @@
       <c r="R8" s="5" t="inlineStr"/>
       <c r="S8" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1428,7 @@
       <c r="M9" s="2" t="inlineStr"/>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1399,7 +1445,7 @@
       <c r="R9" s="5" t="inlineStr"/>
       <c r="S9" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1449,7 +1495,7 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1466,7 +1512,7 @@
       <c r="R10" s="5" t="inlineStr"/>
       <c r="S10" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1562,7 @@
       <c r="M11" s="2" t="inlineStr"/>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
@@ -1533,7 +1579,7 @@
       <c r="R11" s="5" t="inlineStr"/>
       <c r="S11" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1583,7 +1629,7 @@
       <c r="M12" s="2" t="inlineStr"/>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
@@ -1600,7 +1646,7 @@
       <c r="R12" s="5" t="inlineStr"/>
       <c r="S12" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1650,7 +1696,7 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1667,7 +1713,7 @@
       <c r="R13" s="5" t="inlineStr"/>
       <c r="S13" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1759,7 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Odluka o prikazu SISTEMA ONYX HD TROPICAL (nema jednu ambalažu): npr. bez fotografije, zvanična slika sistema/kolekcije ili konkretna komponenta — NE fotografisati jednu limenku</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1730,7 +1776,7 @@
       <c r="R14" s="5" t="inlineStr"/>
       <c r="S14" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — čeka odluku o prikazu sistema</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1826,7 @@
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
@@ -1797,7 +1843,7 @@
       <c r="R15" s="5" t="inlineStr"/>
       <c r="S15" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1893,7 @@
       <c r="M16" s="2" t="inlineStr"/>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -1864,7 +1910,7 @@
       <c r="R16" s="5" t="inlineStr"/>
       <c r="S16" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1914,7 +1960,7 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
@@ -1931,7 +1977,7 @@
       <c r="R17" s="5" t="inlineStr"/>
       <c r="S17" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -1981,7 +2027,7 @@
       <c r="M18" s="2" t="inlineStr"/>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
@@ -1998,7 +2044,7 @@
       <c r="R18" s="5" t="inlineStr"/>
       <c r="S18" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -2111,7 +2157,7 @@
       <c r="M20" s="2" t="inlineStr"/>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -2128,7 +2174,7 @@
       <c r="R20" s="5" t="inlineStr"/>
       <c r="S20" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2224,7 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2195,7 +2241,7 @@
       <c r="R21" s="5" t="inlineStr"/>
       <c r="S21" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2291,7 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -2262,7 +2308,7 @@
       <c r="R22" s="5" t="inlineStr"/>
       <c r="S22" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -2316,7 +2362,7 @@
       <c r="M23" s="2" t="inlineStr"/>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
@@ -2333,7 +2379,7 @@
       <c r="R23" s="5" t="inlineStr"/>
       <c r="S23" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2433,7 @@
       <c r="M24" s="2" t="inlineStr"/>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
@@ -2404,7 +2450,7 @@
       <c r="R24" s="5" t="inlineStr"/>
       <c r="S24" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2504,7 @@
       <c r="M25" s="2" t="inlineStr"/>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -2475,7 +2521,7 @@
       <c r="R25" s="5" t="inlineStr"/>
       <c r="S25" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -2529,7 +2575,7 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Vaša fotografija ambalaže (proizvođač ne objavljuje sliku ove šifre)</t>
+          <t>Vaša fotografija ambalaže, ako je artikal u našoj ponudi (proizvođač ne objavljuje sliku ove šifre)</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
@@ -2546,7 +2592,7 @@
       <c r="R26" s="5" t="inlineStr"/>
       <c r="S26" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -6768,7 +6814,7 @@
       </c>
       <c r="S72" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
         </is>
       </c>
     </row>
@@ -8078,7 +8124,7 @@
       </c>
       <c r="S86" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
         </is>
       </c>
     </row>
@@ -8173,7 +8219,7 @@
       </c>
       <c r="S87" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9929,7 @@
       </c>
       <c r="S105" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10784,7 @@
       </c>
       <c r="S114" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
         </is>
       </c>
     </row>
@@ -10833,7 +10879,7 @@
       </c>
       <c r="S115" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11619,7 @@
       <c r="R123" s="5" t="inlineStr"/>
       <c r="S123" s="5" t="inlineStr">
         <is>
-          <t>nije pronađeno — potrebna Vaša fotografija</t>
+          <t>nije pronađeno — potrebna Vaša fotografija (ako je u ponudi)</t>
         </is>
       </c>
     </row>
@@ -13868,7 +13914,7 @@
       </c>
       <c r="S148" s="5" t="inlineStr">
         <is>
-          <t>pronađeno — čeka pravo i potvrdu varijante</t>
+          <t>kandidat (slika srodnog artikla) — bez uvoza dok se ne potvrdi šta prikazuje; čeka i pravo</t>
         </is>
       </c>
     </row>
